--- a/Data/collapsed database manual cases/oaxaca_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/oaxaca_collapsed_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BC2177-40E7-4442-8650-7AF1CFAFE67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A27065-3DAE-0844-93E4-A3DBC835A829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10341" uniqueCount="2201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10369" uniqueCount="2213">
   <si>
     <t>uniqueid</t>
   </si>
@@ -6627,6 +6627,42 @@
   </si>
   <si>
     <t>https://ieepco.org.mx/computo2022_ext/index.html</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS GARCIA SALUD</t>
+  </si>
+  <si>
+    <t>https://www.meganoticias.mx/salina-cruz/noticia/recibe-constancia-de-mayoria-de-votos-juan-carlos-salud/317956</t>
+  </si>
+  <si>
+    <t>URYEL BAUTISTA VASQUEZ</t>
+  </si>
+  <si>
+    <t>MOISES CASTRO MONTESINOS</t>
+  </si>
+  <si>
+    <t>https://www.ieepco.org.mx/archivos/Gaceta/2022/A1IEEPCOCG492022.pdf</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/share/p/1Kb8v5bvx8/</t>
+  </si>
+  <si>
+    <t>ARACELY GARCIA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>FREDDY GIL PINEDA GOPAR</t>
+  </si>
+  <si>
+    <t>OSCAR SANCHEZ GUERRA</t>
+  </si>
+  <si>
+    <t>JL</t>
+  </si>
+  <si>
+    <t>https://www.congresooaxaca.gob.mx/LXV/dips/33.html</t>
+  </si>
+  <si>
+    <t>https://www.google.com/url?sa=t&amp;source=web&amp;rct=j&amp;opi=89978449&amp;url=https://pri.org.mx/bancoinformacion/Files/Archivos/Excel/30260-7-14_28_35.xlsx&amp;ved=2ahUKEwibsZaopLeTAxXPI0QIHebGO6gQFnoECDAQAQ&amp;usg=AOvVaw3VrFRnhFYiRshi63-9ctQr</t>
   </si>
 </sst>
 </file>
@@ -6987,7 +7023,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S1205"/>
+  <dimension ref="A1:S1212"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="20.1640625" bestFit="1" customWidth="1"/>
@@ -53892,6 +53928,146 @@
       </c>
       <c r="H1205" t="s">
         <v>94</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1206">
+        <v>20421</v>
+      </c>
+      <c r="B1206">
+        <v>2024</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1206" t="s">
+        <v>2201</v>
+      </c>
+      <c r="H1206" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1206" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1207">
+        <v>20421</v>
+      </c>
+      <c r="B1207">
+        <v>2022</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>2066</v>
+      </c>
+      <c r="F1207" t="s">
+        <v>2203</v>
+      </c>
+      <c r="H1207" t="s">
+        <v>151</v>
+      </c>
+      <c r="I1207" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1208">
+        <v>20549</v>
+      </c>
+      <c r="B1208">
+        <v>2021</v>
+      </c>
+      <c r="E1208" t="s">
+        <v>2066</v>
+      </c>
+      <c r="F1208" t="s">
+        <v>2204</v>
+      </c>
+      <c r="H1208" t="s">
+        <v>151</v>
+      </c>
+      <c r="I1208" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1209">
+        <v>20075</v>
+      </c>
+      <c r="B1209">
+        <v>2022</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1209" t="s">
+        <v>2207</v>
+      </c>
+      <c r="H1209" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1209" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1210">
+        <v>20319</v>
+      </c>
+      <c r="B1210">
+        <v>2021</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1210" t="s">
+        <v>2208</v>
+      </c>
+      <c r="H1210" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1210" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1211">
+        <v>20441</v>
+      </c>
+      <c r="B1211">
+        <v>2022</v>
+      </c>
+      <c r="E1211" t="s">
+        <v>2072</v>
+      </c>
+      <c r="F1211" t="s">
+        <v>2209</v>
+      </c>
+      <c r="H1211" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1211" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1212">
+        <v>20472</v>
+      </c>
+      <c r="B1212">
+        <v>2022</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>2072</v>
+      </c>
+      <c r="F1212" t="s">
+        <v>1711</v>
+      </c>
+      <c r="H1212" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1212" t="s">
+        <v>2212</v>
       </c>
     </row>
   </sheetData>
